--- a/data/trans_dic/IQ2605_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ2605_R2-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84,45%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>55,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>67,64%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>80,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,45%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,44; 64,44</t>
+          <t>45,48; 61,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,13; 75,67</t>
+          <t>64,25; 79,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,11; 87,03</t>
+          <t>77,3; 89,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,06; 85,34</t>
+          <t>60,28; 87,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,84; 61,28</t>
+          <t>48,11; 63,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,99; 79,7</t>
+          <t>58,49; 75,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,83; 89,58</t>
+          <t>70,58; 87,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,37; 85,78</t>
+          <t>58,75; 84,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,59; 60,12</t>
+          <t>49,85; 60,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,48; 75,31</t>
+          <t>63,36; 75,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,05; 87,24</t>
+          <t>77,92; 87,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,49; 82,93</t>
+          <t>62,98; 82,98</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>72,85%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>61,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>77,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>78,59%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,1%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,06%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,24; 69,38</t>
+          <t>50,9; 68,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,79; 83,9</t>
+          <t>56,85; 73,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,7; 84,41</t>
+          <t>79,77; 90,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,41; 83,51</t>
+          <t>50,77; 87,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,49; 68,42</t>
+          <t>52,27; 70,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,84; 73,8</t>
+          <t>69,85; 83,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 90,83</t>
+          <t>71,31; 84,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,68; 86,55</t>
+          <t>56,56; 83,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,18; 66,3</t>
+          <t>53,63; 66,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,94; 76,82</t>
+          <t>65,8; 76,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,5; 86,97</t>
+          <t>77,95; 86,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,62; 81,89</t>
+          <t>60,53; 83,28</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64,15%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>53,09%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>73,88%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>69,87%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,2%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,05%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,11; 62,73</t>
+          <t>47,08; 62,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,75; 81,14</t>
+          <t>64,18; 80,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,65; 79,44</t>
+          <t>69,9; 85,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 75,66</t>
+          <t>41,22; 80,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,55; 63,26</t>
+          <t>42,69; 63,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,18; 80,52</t>
+          <t>65,25; 81,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,81; 84,44</t>
+          <t>59,87; 78,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,23; 80,77</t>
+          <t>28,57; 76,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,6; 60,21</t>
+          <t>48,15; 61,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,52; 78,53</t>
+          <t>67,97; 78,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,96; 80,15</t>
+          <t>67,88; 80,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,5; 73,8</t>
+          <t>43,66; 73,67</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>58,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>74,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>75,31%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 64,05</t>
+          <t>46,05; 57,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,05; 79,05</t>
+          <t>74,95; 84,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,45; 79,69</t>
+          <t>72,83; 82,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,74; 81,09</t>
+          <t>71,27; 92,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,1; 57,44</t>
+          <t>53,54; 64,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,87; 83,54</t>
+          <t>68,55; 78,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,89; 82,43</t>
+          <t>70,63; 79,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,67; 93,07</t>
+          <t>55,03; 79,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,45; 59,25</t>
+          <t>51,01; 59,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,05</t>
+          <t>73,24; 80,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,08; 79,96</t>
+          <t>73,26; 79,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,19; 84,82</t>
+          <t>67,16; 83,79</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50,37%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79,9%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>81,42%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>50,52%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>71,85%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>76,27%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,37%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,98; 58,78</t>
+          <t>42,79; 57,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,68; 77,49</t>
+          <t>62,54; 75,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,48; 81,22</t>
+          <t>73,94; 85,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,99; 92,96</t>
+          <t>68,61; 90,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,06; 57,31</t>
+          <t>42,13; 58,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,72; 75,9</t>
+          <t>65,2; 78,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,3; 85,16</t>
+          <t>69,67; 81,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,35; 90,53</t>
+          <t>60,78; 91,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,28; 55,7</t>
+          <t>44,69; 55,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,6; 74,74</t>
+          <t>65,6; 74,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,98; 82,07</t>
+          <t>73,81; 82,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,69; 89,29</t>
+          <t>70,52; 88,24</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71,03%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>40,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>76,13%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>71,99%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,46; 49,91</t>
+          <t>36,53; 55,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,32; 85,08</t>
+          <t>66,89; 84,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,2; 79,74</t>
+          <t>54,16; 73,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,06; 89,28</t>
+          <t>49,7; 85,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,22; 54,9</t>
+          <t>30,43; 49,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,33; 84,18</t>
+          <t>65,3; 85,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,51; 73,53</t>
+          <t>61,36; 80,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,1; 86,4</t>
+          <t>40,78; 88,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,0; 49,71</t>
+          <t>36,05; 49,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,74; 82,46</t>
+          <t>69,48; 82,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60,6; 74,36</t>
+          <t>60,2; 74,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,88; 83,27</t>
+          <t>56,25; 83,53</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52,76%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73,54%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79,27%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77,04%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>54,49%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>73,37%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>75,86%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>71,82%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,37; 58,1</t>
+          <t>49,79; 55,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,41; 76,02</t>
+          <t>70,94; 76,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,37; 78,68</t>
+          <t>76,84; 81,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65,08; 77,69</t>
+          <t>71,35; 82,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,75; 55,82</t>
+          <t>51,06; 57,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,76; 76,2</t>
+          <t>70,51; 76,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,65; 81,71</t>
+          <t>72,97; 78,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,02; 82,54</t>
+          <t>64,84; 76,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,43; 55,92</t>
+          <t>51,34; 56,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,51; 75,4</t>
+          <t>71,52; 75,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75,66; 79,39</t>
+          <t>75,7; 79,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,57; 78,58</t>
+          <t>69,56; 78,37</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50916</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61456</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82057</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27766</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>56569</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>58608</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>64581</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22315</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50916</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61456</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82057</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>22202</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>49969</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48968; 65144</t>
+          <t>43197; 58799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50364; 65563</t>
+          <t>54727; 68011</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58466; 69601</t>
+          <t>75105; 86696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17761; 25665</t>
+          <t>22173; 32156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42590; 58209</t>
+          <t>48634; 64414</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54505; 67886</t>
+          <t>50683; 65234</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75625; 87041</t>
+          <t>56441; 69611</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21991; 32316</t>
+          <t>17698; 25536</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95278; 117866</t>
+          <t>97739; 119409</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110792; 129406</t>
+          <t>108863; 128968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138253; 154541</t>
+          <t>138033; 154653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43694; 56185</t>
+          <t>42137; 55521</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51672</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61506</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95871</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14504</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51450</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>70733</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>80382</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17481</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51672</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61506</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95871</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32736</t>
+          <t>32516</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44018; 58460</t>
+          <t>43761; 58904</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63729; 76618</t>
+          <t>53069; 68415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72309; 86335</t>
+          <t>88868; 100979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13496; 20340</t>
+          <t>10108; 17459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44267; 58823</t>
+          <t>44039; 59141</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53992; 68890</t>
+          <t>63787; 76544</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89054; 101185</t>
+          <t>72934; 86508</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11406; 18390</t>
+          <t>14067; 20838</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92236; 112869</t>
+          <t>91300; 113057</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121760; 141864</t>
+          <t>121512; 141900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167736; 185836</t>
+          <t>166573; 184594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27190; 37346</t>
+          <t>27108; 37293</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53984</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60822</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57831</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10414</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>35067</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>61050</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>43208</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6034</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53984</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60822</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57831</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>16769</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27820; 41437</t>
+          <t>46084; 61543</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54327; 67045</t>
+          <t>53165; 66893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36889; 49127</t>
+          <t>51796; 63200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3076; 8745</t>
+          <t>6692; 13024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46542; 61915</t>
+          <t>28200; 41834</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53165; 66703</t>
+          <t>53919; 67189</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50988; 62571</t>
+          <t>37022; 48449</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7637; 14271</t>
+          <t>3385; 9023</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78038; 98712</t>
+          <t>78931; 100050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111736; 129944</t>
+          <t>112477; 130686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92378; 108956</t>
+          <t>92275; 108868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12713; 21569</t>
+          <t>12260; 20686</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>102160</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173202</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163800</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>115448</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>147392</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>165769</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26528</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>102160</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>173202</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>163800</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39362</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65889</t>
+          <t>60561</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103702; 125662</t>
+          <t>90468; 112922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137267; 157140</t>
+          <t>163672; 183649</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>155055; 175397</t>
+          <t>152680; 173014</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21652; 30944</t>
+          <t>30198; 38989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90556; 112838</t>
+          <t>105043; 126897</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>161328; 182431</t>
+          <t>136263; 156958</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>152797; 172800</t>
+          <t>155467; 175929</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33947; 43474</t>
+          <t>19959; 28911</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202022; 232616</t>
+          <t>200296; 233221</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>306012; 333957</t>
+          <t>305548; 334573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>314067; 343598</t>
+          <t>314820; 342841</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57879; 71993</t>
+          <t>52812; 65892</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>62743</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>95713</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32157</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>51249</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>103634</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>102614</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19073</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>62743</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95713</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>113536</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>48176</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43600; 59632</t>
+          <t>53305; 71735</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93292; 111763</t>
+          <t>86724; 105203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93475; 109270</t>
+          <t>105069; 121302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15067; 21553</t>
+          <t>27096; 35698</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53634; 71386</t>
+          <t>42733; 59025</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85591; 105257</t>
+          <t>94037; 112635</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>105585; 121009</t>
+          <t>93727; 110201</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28642; 37935</t>
+          <t>12120; 18305</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>102327; 125878</t>
+          <t>101005; 125505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185603; 211459</t>
+          <t>185582; 211503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204643; 227049</t>
+          <t>204198; 227170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47314; 58113</t>
+          <t>41911; 52446</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>31650</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>54144</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>43531</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>29734</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>39141</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9367</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>31650</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>54144</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>43531</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>24485</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23311; 36986</t>
+          <t>25387; 38453</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33070; 43742</t>
+          <t>47319; 59564</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37023; 48233</t>
+          <t>36732; 50053</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5605; 11623</t>
+          <t>10346; 17819</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24481; 38156</t>
+          <t>22552; 36546</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47632; 59553</t>
+          <t>33573; 43805</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36969; 49874</t>
+          <t>37119; 48784</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12503; 20344</t>
+          <t>5570; 12022</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51693; 71384</t>
+          <t>51765; 71018</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85193; 100734</t>
+          <t>84873; 100188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77764; 95411</t>
+          <t>77244; 95102</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21162; 30445</t>
+          <t>19391; 28795</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>697</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>761</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>160</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>353125</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>506842</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>556626</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135294</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>339518</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>480558</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>500098</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>100798</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>353125</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>506842</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>556626</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>145493</t>
+          <t>97181</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>246292</t>
+          <t>232475</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>320124; 362036</t>
+          <t>333251; 373855</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>461182; 497936</t>
+          <t>488898; 524639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>483681; 518663</t>
+          <t>539603; 573917</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91343; 109043</t>
+          <t>125302; 144037</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>333026; 373592</t>
+          <t>318177; 359425</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>487626; 525135</t>
+          <t>461854; 499064</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>538228; 573762</t>
+          <t>481015; 518455</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>134043; 155795</t>
+          <t>88644; 105087</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>664755; 722720</t>
+          <t>663562; 723885</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>961215; 1013586</t>
+          <t>961361; 1011490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1030116; 1080796</t>
+          <t>1030671; 1081729</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>232255; 258604</t>
+          <t>217256; 244748</t>
         </is>
       </c>
     </row>
